--- a/财务与流水/馋唻买-听涛路店工资表.xlsx
+++ b/财务与流水/馋唻买-听涛路店工资表.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="15800"/>
+    <workbookView windowHeight="15820"/>
   </bookViews>
   <sheets>
     <sheet name="工资绩效说明" sheetId="1" r:id="rId1"/>
@@ -16,12 +16,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="96">
   <si>
     <t>员工工资绩效制度说明</t>
   </si>
   <si>
-    <t>一、基础工资</t>
+    <t>方案一(基础工资+绩效)：</t>
+  </si>
+  <si>
+    <t>基础工资</t>
   </si>
   <si>
     <t>职位</t>
@@ -33,58 +36,79 @@
     <t>店长</t>
   </si>
   <si>
-    <t>6000元</t>
+    <t>6500元</t>
   </si>
   <si>
     <t>员工</t>
   </si>
   <si>
+    <t>5000元</t>
+  </si>
+  <si>
+    <t>绩效奖励</t>
+  </si>
+  <si>
+    <t>营业额区间</t>
+  </si>
+  <si>
+    <t>每人奖励</t>
+  </si>
+  <si>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>≥2000元</t>
+  </si>
+  <si>
+    <t>10/天</t>
+  </si>
+  <si>
+    <t>堂食+外卖平台总收入</t>
+  </si>
+  <si>
+    <t>≥2500元</t>
+  </si>
+  <si>
+    <t>20/天</t>
+  </si>
+  <si>
+    <t>≥3000元</t>
+  </si>
+  <si>
+    <t>30/天</t>
+  </si>
+  <si>
+    <t>≥3500元</t>
+  </si>
+  <si>
+    <t>40/天</t>
+  </si>
+  <si>
+    <t>≥4000元</t>
+  </si>
+  <si>
+    <t>50/天</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>月度绩效最多1550元（50元 × 31天）</t>
+  </si>
+  <si>
+    <t>方案二(固定工资)：</t>
+  </si>
+  <si>
+    <t>一、固定工资</t>
+  </si>
+  <si>
+    <t>7000元</t>
+  </si>
+  <si>
     <t>5500元</t>
   </si>
   <si>
-    <t>二、绩效奖励</t>
-  </si>
-  <si>
-    <t>营业额区间</t>
-  </si>
-  <si>
-    <t>每人奖励</t>
-  </si>
-  <si>
-    <t>说明</t>
-  </si>
-  <si>
-    <t>≥2500元</t>
-  </si>
-  <si>
-    <t>10元</t>
-  </si>
-  <si>
-    <t>堂食+外卖平台总收入</t>
-  </si>
-  <si>
-    <t>≥3000元</t>
-  </si>
-  <si>
-    <t>30元</t>
-  </si>
-  <si>
-    <t>≥3500元</t>
-  </si>
-  <si>
-    <t>50元（上限）</t>
-  </si>
-  <si>
-    <t>绩效上限为50元/天</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>月度绩效最多1550元（50元 × 31天）</t>
-  </si>
-  <si>
-    <t>三、处罚规则</t>
+    <t>处罚规则(后期执行)</t>
   </si>
   <si>
     <t>情形</t>
@@ -123,16 +147,7 @@
     <t>-25/小时</t>
   </si>
   <si>
-    <t>年终奖</t>
-  </si>
-  <si>
-    <t>待定</t>
-  </si>
-  <si>
-    <t>根据全年营收发放，不保证</t>
-  </si>
-  <si>
-    <t>四、工作时间安排</t>
+    <t>工作时间安排</t>
   </si>
   <si>
     <t>工作时间</t>
@@ -141,34 +156,19 @@
     <t>员工A</t>
   </si>
   <si>
-    <t>8:00-12:00 + 16:00-20:00</t>
-  </si>
-  <si>
-    <t>8小时制</t>
+    <t>11:00-13:00 + 19:00-02:00</t>
+  </si>
+  <si>
+    <t>9小时制</t>
   </si>
   <si>
     <t>员工B</t>
   </si>
   <si>
-    <t>11:00-13:00 + 18:00-24:00</t>
-  </si>
-  <si>
-    <t>高峰期</t>
-  </si>
-  <si>
-    <t>11:00-13:00 + 18:00-20:00</t>
-  </si>
-  <si>
-    <t>员工A和B共同在岗</t>
-  </si>
-  <si>
-    <t>非高峰期</t>
-  </si>
-  <si>
-    <t>其他时间</t>
-  </si>
-  <si>
-    <t>根据时间段单独值班</t>
+    <t>8:00-13:00 + 16:00-20:00</t>
+  </si>
+  <si>
+    <t>员工C</t>
   </si>
   <si>
     <t>2026年2月份工资明细表</t>
@@ -181,12 +181,6 @@
   </si>
   <si>
     <t>员工名称</t>
-  </si>
-  <si>
-    <t>基础工资</t>
-  </si>
-  <si>
-    <t>绩效奖励</t>
   </si>
   <si>
     <t>处罚扣款</t>
@@ -317,12 +311,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -361,9 +355,115 @@
     </font>
     <font>
       <b/>
+      <sz val="16"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="14"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -375,7 +475,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -390,63 +490,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -458,13 +504,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -474,15 +513,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -495,28 +526,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="36">
     <fill>
@@ -551,181 +560,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -742,17 +751,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -768,6 +768,39 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -798,30 +831,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -839,152 +848,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -998,7 +1007,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1346,7 +1358,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="35.4134615384615" customWidth="1"/>
@@ -1354,223 +1366,280 @@
     <col min="3" max="3" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.4" spans="1:1">
+    <row r="1" ht="23.2" spans="1:4">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="2" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+    </row>
+    <row r="2" ht="20.4" spans="1:1">
+      <c r="A2" s="10"/>
+    </row>
+    <row r="3" ht="20.4" spans="1:1">
+      <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
+    <row r="4" spans="1:1">
+      <c r="A4" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" t="s">
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="2" t="s">
+      <c r="B7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="9" t="s">
+    <row r="9" spans="1:1">
+      <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="9" t="s">
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="B10" s="11" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
+      <c r="C10" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B10" t="s">
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
         <v>13</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
+      <c r="C11" t="s">
         <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
         <v>17</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
         <v>18</v>
       </c>
-      <c r="C12" t="s">
+      <c r="B13" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
         <v>20</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="2" t="s">
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="9" t="s">
+      <c r="B15" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
+      <c r="B16" t="s">
         <v>25</v>
       </c>
-      <c r="B17" t="s">
+    </row>
+    <row r="18" customFormat="1" ht="20.4" spans="1:1">
+      <c r="A18" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C17" t="s">
+    </row>
+    <row r="19" customFormat="1" spans="1:1">
+      <c r="A19" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
+    <row r="20" customFormat="1" spans="1:2">
+      <c r="A20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" spans="1:2">
+      <c r="A21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" t="s">
         <v>28</v>
       </c>
-      <c r="B18" t="s">
+    </row>
+    <row r="22" customFormat="1" spans="1:2">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" t="s">
         <v>29</v>
       </c>
-      <c r="C18" t="s">
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="2"/>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="2"/>
+    </row>
+    <row r="25" ht="20.4" spans="1:1">
+      <c r="A25" s="12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
+    <row r="26" spans="1:3">
+      <c r="A26" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B26" s="11" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" t="s">
-        <v>41</v>
-      </c>
-      <c r="C25" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" t="s">
-        <v>42</v>
+      <c r="C26" s="11" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C27" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="2"/>
+    </row>
+    <row r="33" ht="20.4" spans="1:1">
+      <c r="A33" s="12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
         <v>48</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B36" t="s">
         <v>49</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C36" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
         <v>50</v>
+      </c>
+      <c r="B37" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B16:C16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1608,30 +1677,30 @@
         <v>54</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6">
         <v>6000</v>
@@ -1647,10 +1716,10 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7">
         <v>5500</v>
@@ -1666,23 +1735,23 @@
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C11">
         <f t="shared" ref="C11:C38" si="0">IF(B11&gt;=3500,50,IF(B11&gt;=3000,30,IF(B11&gt;=2500,10,0)))</f>
@@ -1691,7 +1760,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -1700,7 +1769,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -1709,7 +1778,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -1718,7 +1787,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -1727,7 +1796,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -1736,7 +1805,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -1745,7 +1814,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
@@ -1754,7 +1823,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
@@ -1763,7 +1832,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
@@ -1772,7 +1841,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
@@ -1781,7 +1850,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C22">
         <f t="shared" si="0"/>
@@ -1790,7 +1859,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C23">
         <f t="shared" si="0"/>
@@ -1799,7 +1868,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C24">
         <f t="shared" si="0"/>
@@ -1808,7 +1877,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C25">
         <f t="shared" si="0"/>
@@ -1817,7 +1886,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C26">
         <f t="shared" si="0"/>
@@ -1826,7 +1895,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C27">
         <f t="shared" si="0"/>
@@ -1835,7 +1904,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C28">
         <f t="shared" si="0"/>
@@ -1844,7 +1913,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C29">
         <f t="shared" si="0"/>
@@ -1853,7 +1922,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C30">
         <f t="shared" si="0"/>
@@ -1862,7 +1931,7 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C31">
         <f t="shared" si="0"/>
@@ -1871,7 +1940,7 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C32">
         <f t="shared" si="0"/>
@@ -1880,7 +1949,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C33">
         <f t="shared" si="0"/>
@@ -1889,7 +1958,7 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C34">
         <f t="shared" si="0"/>
@@ -1898,7 +1967,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C35">
         <f t="shared" si="0"/>
@@ -1907,7 +1976,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C36">
         <f t="shared" si="0"/>
@@ -1916,7 +1985,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C37">
         <f t="shared" si="0"/>
@@ -1925,7 +1994,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C38">
         <f t="shared" si="0"/>
@@ -1934,7 +2003,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C39" s="2">
         <f>SUM(C11:C38)</f>
@@ -1943,23 +2012,23 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C42" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C43">
         <f t="shared" ref="C43:C70" si="1">IF(B43&gt;=3500,50,IF(B43&gt;=3000,30,IF(B43&gt;=2500,10,0)))</f>
@@ -1968,7 +2037,7 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C44">
         <f t="shared" si="1"/>
@@ -1977,7 +2046,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C45">
         <f t="shared" si="1"/>
@@ -1986,7 +2055,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C46">
         <f t="shared" si="1"/>
@@ -1995,7 +2064,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C47">
         <f t="shared" si="1"/>
@@ -2004,7 +2073,7 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C48">
         <f t="shared" si="1"/>
@@ -2013,7 +2082,7 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C49">
         <f t="shared" si="1"/>
@@ -2022,7 +2091,7 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C50">
         <f t="shared" si="1"/>
@@ -2031,7 +2100,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C51">
         <f t="shared" si="1"/>
@@ -2040,7 +2109,7 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C52">
         <f t="shared" si="1"/>
@@ -2049,7 +2118,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C53">
         <f t="shared" si="1"/>
@@ -2058,7 +2127,7 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C54">
         <f t="shared" si="1"/>
@@ -2067,7 +2136,7 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C55">
         <f t="shared" si="1"/>
@@ -2076,7 +2145,7 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C56">
         <f t="shared" si="1"/>
@@ -2085,7 +2154,7 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C57">
         <f t="shared" si="1"/>
@@ -2094,7 +2163,7 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C58">
         <f t="shared" si="1"/>
@@ -2103,7 +2172,7 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C59">
         <f t="shared" si="1"/>
@@ -2112,7 +2181,7 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C60">
         <f t="shared" si="1"/>
@@ -2121,7 +2190,7 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C61">
         <f t="shared" si="1"/>
@@ -2130,7 +2199,7 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C62">
         <f t="shared" si="1"/>
@@ -2139,7 +2208,7 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C63">
         <f t="shared" si="1"/>
@@ -2148,7 +2217,7 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C64">
         <f t="shared" si="1"/>
@@ -2157,7 +2226,7 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C65">
         <f t="shared" si="1"/>
@@ -2166,7 +2235,7 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C66">
         <f t="shared" si="1"/>
@@ -2175,7 +2244,7 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C67">
         <f t="shared" si="1"/>
@@ -2184,7 +2253,7 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C68">
         <f t="shared" si="1"/>
@@ -2193,7 +2262,7 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C69">
         <f t="shared" si="1"/>
@@ -2202,7 +2271,7 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C70">
         <f t="shared" si="1"/>
@@ -2211,7 +2280,7 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C71" s="2">
         <f>SUM(C43:C70)</f>
@@ -2220,24 +2289,24 @@
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B74" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D74" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C74" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>97</v>
-      </c>
       <c r="E74" s="7" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/财务与流水/馋唻买-听涛路店工资表.xlsx
+++ b/财务与流水/馋唻买-听涛路店工资表.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView windowHeight="15820"/>
+    <workbookView windowHeight="15820" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="工资绩效说明" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="97">
   <si>
     <t>员工工资绩效制度说明</t>
   </si>
@@ -190,6 +190,9 @@
   </si>
   <si>
     <t>实发工资</t>
+  </si>
+  <si>
+    <t>2月未上满扣款</t>
   </si>
   <si>
     <t>绩效奖励明细（员工A）</t>
@@ -312,8 +315,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="28">
@@ -384,7 +387,30 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -394,6 +420,105 @@
       <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -404,128 +529,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="36">
     <fill>
@@ -554,187 +557,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -751,8 +754,32 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -777,45 +804,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -845,156 +833,174 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1367,23 +1373,23 @@
   </cols>
   <sheetData>
     <row r="1" ht="23.2" spans="1:4">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
     </row>
     <row r="2" ht="20.4" spans="1:1">
-      <c r="A2" s="10"/>
+      <c r="A2" s="11"/>
     </row>
     <row r="3" ht="20.4" spans="1:1">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="11" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1412,18 +1418,18 @@
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="12" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1491,12 +1497,12 @@
       </c>
     </row>
     <row r="18" customFormat="1" ht="20.4" spans="1:1">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="19" customFormat="1" spans="1:1">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1525,24 +1531,24 @@
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="2"/>
+      <c r="A23" s="3"/>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="2"/>
+      <c r="A24" s="3"/>
     </row>
     <row r="25" ht="20.4" spans="1:1">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="13" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="12" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1572,7 +1578,7 @@
       <c r="A29" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="14" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1580,26 +1586,26 @@
       <c r="A30" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="14" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="2"/>
+      <c r="A32" s="3"/>
     </row>
     <row r="33" ht="20.4" spans="1:1">
-      <c r="A33" s="12" t="s">
+      <c r="A33" s="13" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="7" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1650,15 +1656,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G74"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
+  <dimension ref="A1:H74"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
     <col min="3" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="29.4807692307692" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.6" spans="1:1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1668,90 +1675,105 @@
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="3" t="s">
+    <row r="5" s="1" customFormat="1" spans="1:8">
+      <c r="A5" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
+      <c r="H5" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:8">
+      <c r="A6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6">
-        <v>6000</v>
-      </c>
-      <c r="D6">
+      <c r="C6" s="1">
+        <v>7000</v>
+      </c>
+      <c r="D6" s="1">
         <f>C39</f>
         <v>0</v>
       </c>
-      <c r="G6">
+      <c r="F6" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G6" s="1">
         <f>C6+D6-E6-F6</f>
         <v>6000</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
+      <c r="H6" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:8">
+      <c r="A7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7">
-        <v>5500</v>
-      </c>
-      <c r="D7">
+      <c r="C7" s="1">
+        <v>5000</v>
+      </c>
+      <c r="D7" s="1">
         <f>C71</f>
         <v>0</v>
       </c>
-      <c r="G7">
+      <c r="F7" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G7" s="1">
         <f>C7+D7-E7-F7</f>
-        <v>5500</v>
+        <v>4000</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="4" t="s">
-        <v>58</v>
+      <c r="A9" s="5" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>61</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C11">
         <f t="shared" ref="C11:C38" si="0">IF(B11&gt;=3500,50,IF(B11&gt;=3000,30,IF(B11&gt;=2500,10,0)))</f>
@@ -1760,7 +1782,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -1769,7 +1791,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -1778,7 +1800,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -1787,7 +1809,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -1796,7 +1818,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -1805,7 +1827,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -1814,7 +1836,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
@@ -1823,7 +1845,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
@@ -1832,7 +1854,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
@@ -1841,7 +1863,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
@@ -1850,7 +1872,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C22">
         <f t="shared" si="0"/>
@@ -1859,7 +1881,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C23">
         <f t="shared" si="0"/>
@@ -1868,7 +1890,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C24">
         <f t="shared" si="0"/>
@@ -1877,7 +1899,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C25">
         <f t="shared" si="0"/>
@@ -1886,7 +1908,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C26">
         <f t="shared" si="0"/>
@@ -1895,7 +1917,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C27">
         <f t="shared" si="0"/>
@@ -1904,7 +1926,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C28">
         <f t="shared" si="0"/>
@@ -1913,7 +1935,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C29">
         <f t="shared" si="0"/>
@@ -1922,7 +1944,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C30">
         <f t="shared" si="0"/>
@@ -1931,7 +1953,7 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C31">
         <f t="shared" si="0"/>
@@ -1940,7 +1962,7 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C32">
         <f t="shared" si="0"/>
@@ -1949,7 +1971,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C33">
         <f t="shared" si="0"/>
@@ -1958,7 +1980,7 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C34">
         <f t="shared" si="0"/>
@@ -1967,7 +1989,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C35">
         <f t="shared" si="0"/>
@@ -1976,7 +1998,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C36">
         <f t="shared" si="0"/>
@@ -1985,7 +2007,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C37">
         <f t="shared" si="0"/>
@@ -1994,7 +2016,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C38">
         <f t="shared" si="0"/>
@@ -2002,33 +2024,36 @@
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C39" s="2">
+      <c r="A39" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C39" s="3">
         <f>SUM(C11:C38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B42" s="6" t="s">
+      <c r="A41" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="B42" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="H42" s="7" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C43">
         <f t="shared" ref="C43:C70" si="1">IF(B43&gt;=3500,50,IF(B43&gt;=3000,30,IF(B43&gt;=2500,10,0)))</f>
@@ -2037,7 +2062,7 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C44">
         <f t="shared" si="1"/>
@@ -2046,7 +2071,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C45">
         <f t="shared" si="1"/>
@@ -2055,7 +2080,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C46">
         <f t="shared" si="1"/>
@@ -2064,7 +2089,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C47">
         <f t="shared" si="1"/>
@@ -2073,7 +2098,7 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C48">
         <f t="shared" si="1"/>
@@ -2082,7 +2107,7 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C49">
         <f t="shared" si="1"/>
@@ -2091,7 +2116,7 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C50">
         <f t="shared" si="1"/>
@@ -2100,7 +2125,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C51">
         <f t="shared" si="1"/>
@@ -2109,7 +2134,7 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C52">
         <f t="shared" si="1"/>
@@ -2118,7 +2143,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C53">
         <f t="shared" si="1"/>
@@ -2127,7 +2152,7 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C54">
         <f t="shared" si="1"/>
@@ -2136,7 +2161,7 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C55">
         <f t="shared" si="1"/>
@@ -2145,7 +2170,7 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C56">
         <f t="shared" si="1"/>
@@ -2154,7 +2179,7 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C57">
         <f t="shared" si="1"/>
@@ -2163,7 +2188,7 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C58">
         <f t="shared" si="1"/>
@@ -2172,7 +2197,7 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C59">
         <f t="shared" si="1"/>
@@ -2181,7 +2206,7 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C60">
         <f t="shared" si="1"/>
@@ -2190,7 +2215,7 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C61">
         <f t="shared" si="1"/>
@@ -2199,7 +2224,7 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C62">
         <f t="shared" si="1"/>
@@ -2208,7 +2233,7 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C63">
         <f t="shared" si="1"/>
@@ -2217,7 +2242,7 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C64">
         <f t="shared" si="1"/>
@@ -2226,7 +2251,7 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C65">
         <f t="shared" si="1"/>
@@ -2235,7 +2260,7 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C66">
         <f t="shared" si="1"/>
@@ -2244,7 +2269,7 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C67">
         <f t="shared" si="1"/>
@@ -2253,7 +2278,7 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C68">
         <f t="shared" si="1"/>
@@ -2262,7 +2287,7 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C69">
         <f t="shared" si="1"/>
@@ -2271,7 +2296,7 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C70">
         <f t="shared" si="1"/>
@@ -2279,34 +2304,37 @@
       </c>
     </row>
     <row r="71" spans="1:3">
-      <c r="A71" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C71" s="2">
+      <c r="A71" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C71" s="3">
         <f>SUM(C43:C70)</f>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B74" s="7" t="s">
+      <c r="A73" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C74" s="7" t="s">
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B74" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D74" s="7" t="s">
+      <c r="C74" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="E74" s="7" t="s">
+      <c r="D74" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E74" s="8" t="s">
         <v>24</v>
+      </c>
+      <c r="H74" s="8" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/财务与流水/馋唻买-听涛路店工资表.xlsx
+++ b/财务与流水/馋唻买-听涛路店工资表.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView windowHeight="15820" activeTab="1"/>
+    <workbookView windowHeight="17020"/>
   </bookViews>
   <sheets>
     <sheet name="工资绩效说明" sheetId="1" r:id="rId1"/>
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="96">
   <si>
     <t>员工工资绩效制度说明</t>
   </si>
   <si>
-    <t>方案一(基础工资+绩效)：</t>
+    <t>方案一(基础工资+绩效奖励)：</t>
   </si>
   <si>
     <t>基础工资</t>
@@ -90,223 +90,220 @@
     <t>50/天</t>
   </si>
   <si>
+    <t>方案二(固定工资)：</t>
+  </si>
+  <si>
+    <t>一、固定工资</t>
+  </si>
+  <si>
+    <t>7000元</t>
+  </si>
+  <si>
+    <t>5500元</t>
+  </si>
+  <si>
+    <t>处罚规则(四月份开始试行)</t>
+  </si>
+  <si>
+    <t>情形</t>
+  </si>
+  <si>
+    <t>处罚金额</t>
+  </si>
+  <si>
+    <t>差评/退单/退款（有责任人）</t>
+  </si>
+  <si>
+    <t>-10元/次</t>
+  </si>
+  <si>
+    <t>职责明确时，责任人承担</t>
+  </si>
+  <si>
+    <t>差评/退单/退款（无法明确）</t>
+  </si>
+  <si>
+    <t>平摊</t>
+  </si>
+  <si>
+    <t>所有员工均分处罚</t>
+  </si>
+  <si>
+    <t>请假</t>
+  </si>
+  <si>
+    <t>-200元/天</t>
+  </si>
+  <si>
+    <t>迟到/早退</t>
+  </si>
+  <si>
+    <t>-25/小时</t>
+  </si>
+  <si>
+    <t>工作时间安排</t>
+  </si>
+  <si>
+    <t>工作时间</t>
+  </si>
+  <si>
+    <t>员工A</t>
+  </si>
+  <si>
+    <t>11:00-13:00 + 19:00-02:00</t>
+  </si>
+  <si>
+    <t>9小时制</t>
+  </si>
+  <si>
+    <t>员工B</t>
+  </si>
+  <si>
+    <t>8:00-13:00 + 16:00-20:00</t>
+  </si>
+  <si>
+    <t>员工C</t>
+  </si>
+  <si>
+    <t>2026年2月份工资明细表</t>
+  </si>
+  <si>
+    <t>月份：2026年2月</t>
+  </si>
+  <si>
+    <t>员工工资汇总</t>
+  </si>
+  <si>
+    <t>员工名称</t>
+  </si>
+  <si>
+    <t>处罚扣款</t>
+  </si>
+  <si>
+    <t>其他扣款</t>
+  </si>
+  <si>
+    <t>实发工资</t>
+  </si>
+  <si>
+    <t>2月未上满扣款</t>
+  </si>
+  <si>
+    <t>绩效奖励明细（员工A）</t>
+  </si>
+  <si>
+    <t>日期</t>
+  </si>
+  <si>
+    <t>日营业额(元)</t>
+  </si>
+  <si>
+    <t>绩效奖励(元)</t>
+  </si>
+  <si>
+    <t>2月1日</t>
+  </si>
+  <si>
+    <t>2月2日</t>
+  </si>
+  <si>
+    <t>2月3日</t>
+  </si>
+  <si>
+    <t>2月4日</t>
+  </si>
+  <si>
+    <t>2月5日</t>
+  </si>
+  <si>
+    <t>2月6日</t>
+  </si>
+  <si>
+    <t>2月7日</t>
+  </si>
+  <si>
+    <t>2月8日</t>
+  </si>
+  <si>
+    <t>2月9日</t>
+  </si>
+  <si>
+    <t>2月10日</t>
+  </si>
+  <si>
+    <t>2月11日</t>
+  </si>
+  <si>
+    <t>2月12日</t>
+  </si>
+  <si>
+    <t>2月13日</t>
+  </si>
+  <si>
+    <t>2月14日</t>
+  </si>
+  <si>
+    <t>2月15日</t>
+  </si>
+  <si>
+    <t>2月16日</t>
+  </si>
+  <si>
+    <t>2月17日</t>
+  </si>
+  <si>
+    <t>2月18日</t>
+  </si>
+  <si>
+    <t>2月19日</t>
+  </si>
+  <si>
+    <t>2月20日</t>
+  </si>
+  <si>
+    <t>2月21日</t>
+  </si>
+  <si>
+    <t>2月22日</t>
+  </si>
+  <si>
+    <t>2月23日</t>
+  </si>
+  <si>
+    <t>2月24日</t>
+  </si>
+  <si>
+    <t>2月25日</t>
+  </si>
+  <si>
+    <t>2月26日</t>
+  </si>
+  <si>
+    <t>2月27日</t>
+  </si>
+  <si>
+    <t>2月28日</t>
+  </si>
+  <si>
+    <t>绩效总计</t>
+  </si>
+  <si>
+    <t>绩效奖励明细（员工B）</t>
+  </si>
+  <si>
+    <t>处罚明细</t>
+  </si>
+  <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>责任人</t>
+  </si>
+  <si>
+    <t>金额(元)</t>
+  </si>
+  <si>
     <t>备注</t>
-  </si>
-  <si>
-    <t>月度绩效最多1550元（50元 × 31天）</t>
-  </si>
-  <si>
-    <t>方案二(固定工资)：</t>
-  </si>
-  <si>
-    <t>一、固定工资</t>
-  </si>
-  <si>
-    <t>7000元</t>
-  </si>
-  <si>
-    <t>5500元</t>
-  </si>
-  <si>
-    <t>处罚规则(后期执行)</t>
-  </si>
-  <si>
-    <t>情形</t>
-  </si>
-  <si>
-    <t>处罚金额</t>
-  </si>
-  <si>
-    <t>差评/退单/退款（有责任人）</t>
-  </si>
-  <si>
-    <t>-10元/次</t>
-  </si>
-  <si>
-    <t>职责明确时，责任人承担</t>
-  </si>
-  <si>
-    <t>差评/退单/退款（无法明确）</t>
-  </si>
-  <si>
-    <t>平摊</t>
-  </si>
-  <si>
-    <t>所有员工均分处罚</t>
-  </si>
-  <si>
-    <t>请假</t>
-  </si>
-  <si>
-    <t>-200元/天</t>
-  </si>
-  <si>
-    <t>迟到</t>
-  </si>
-  <si>
-    <t>-25/小时</t>
-  </si>
-  <si>
-    <t>工作时间安排</t>
-  </si>
-  <si>
-    <t>工作时间</t>
-  </si>
-  <si>
-    <t>员工A</t>
-  </si>
-  <si>
-    <t>11:00-13:00 + 19:00-02:00</t>
-  </si>
-  <si>
-    <t>9小时制</t>
-  </si>
-  <si>
-    <t>员工B</t>
-  </si>
-  <si>
-    <t>8:00-13:00 + 16:00-20:00</t>
-  </si>
-  <si>
-    <t>员工C</t>
-  </si>
-  <si>
-    <t>2026年2月份工资明细表</t>
-  </si>
-  <si>
-    <t>月份：2026年2月</t>
-  </si>
-  <si>
-    <t>员工工资汇总</t>
-  </si>
-  <si>
-    <t>员工名称</t>
-  </si>
-  <si>
-    <t>处罚扣款</t>
-  </si>
-  <si>
-    <t>其他扣款</t>
-  </si>
-  <si>
-    <t>实发工资</t>
-  </si>
-  <si>
-    <t>2月未上满扣款</t>
-  </si>
-  <si>
-    <t>绩效奖励明细（员工A）</t>
-  </si>
-  <si>
-    <t>日期</t>
-  </si>
-  <si>
-    <t>日营业额(元)</t>
-  </si>
-  <si>
-    <t>绩效奖励(元)</t>
-  </si>
-  <si>
-    <t>2月1日</t>
-  </si>
-  <si>
-    <t>2月2日</t>
-  </si>
-  <si>
-    <t>2月3日</t>
-  </si>
-  <si>
-    <t>2月4日</t>
-  </si>
-  <si>
-    <t>2月5日</t>
-  </si>
-  <si>
-    <t>2月6日</t>
-  </si>
-  <si>
-    <t>2月7日</t>
-  </si>
-  <si>
-    <t>2月8日</t>
-  </si>
-  <si>
-    <t>2月9日</t>
-  </si>
-  <si>
-    <t>2月10日</t>
-  </si>
-  <si>
-    <t>2月11日</t>
-  </si>
-  <si>
-    <t>2月12日</t>
-  </si>
-  <si>
-    <t>2月13日</t>
-  </si>
-  <si>
-    <t>2月14日</t>
-  </si>
-  <si>
-    <t>2月15日</t>
-  </si>
-  <si>
-    <t>2月16日</t>
-  </si>
-  <si>
-    <t>2月17日</t>
-  </si>
-  <si>
-    <t>2月18日</t>
-  </si>
-  <si>
-    <t>2月19日</t>
-  </si>
-  <si>
-    <t>2月20日</t>
-  </si>
-  <si>
-    <t>2月21日</t>
-  </si>
-  <si>
-    <t>2月22日</t>
-  </si>
-  <si>
-    <t>2月23日</t>
-  </si>
-  <si>
-    <t>2月24日</t>
-  </si>
-  <si>
-    <t>2月25日</t>
-  </si>
-  <si>
-    <t>2月26日</t>
-  </si>
-  <si>
-    <t>2月27日</t>
-  </si>
-  <si>
-    <t>2月28日</t>
-  </si>
-  <si>
-    <t>绩效总计</t>
-  </si>
-  <si>
-    <t>绩效奖励明细（员工B）</t>
-  </si>
-  <si>
-    <t>处罚明细</t>
-  </si>
-  <si>
-    <t>类型</t>
-  </si>
-  <si>
-    <t>责任人</t>
-  </si>
-  <si>
-    <t>金额(元)</t>
   </si>
 </sst>
 </file>
@@ -315,9 +312,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="28">
     <font>
@@ -387,7 +384,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -401,8 +398,53 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -417,14 +459,38 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -438,28 +504,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -468,57 +512,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -557,187 +554,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -754,8 +751,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -764,22 +761,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -802,19 +784,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -830,6 +816,17 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -851,85 +848,85 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -938,37 +935,37 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -977,22 +974,22 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1488,22 +1485,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" t="s">
-        <v>25</v>
-      </c>
-    </row>
     <row r="18" customFormat="1" ht="20.4" spans="1:1">
       <c r="A18" s="11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" customFormat="1" spans="1:1">
       <c r="A19" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" customFormat="1" spans="1:2">
@@ -1519,7 +1508,7 @@
         <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:2">
@@ -1527,7 +1516,7 @@
         <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:1">
@@ -1538,15 +1527,15 @@
     </row>
     <row r="25" ht="20.4" spans="1:1">
       <c r="A25" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>12</v>
@@ -1554,40 +1543,40 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" t="s">
         <v>33</v>
-      </c>
-      <c r="B27" t="s">
-        <v>34</v>
-      </c>
-      <c r="C27" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" t="s">
         <v>36</v>
-      </c>
-      <c r="B28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C28" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:1">
@@ -1595,7 +1584,7 @@
     </row>
     <row r="33" ht="20.4" spans="1:1">
       <c r="A33" s="13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1603,7 +1592,7 @@
         <v>7</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>12</v>
@@ -1611,35 +1600,35 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" t="s">
         <v>45</v>
-      </c>
-      <c r="B35" t="s">
-        <v>46</v>
-      </c>
-      <c r="C35" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C36" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C37" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1666,22 +1655,22 @@
   <sheetData>
     <row r="1" ht="17.6" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:8">
       <c r="A5" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>3</v>
@@ -1693,13 +1682,13 @@
         <v>9</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>12</v>
@@ -1707,7 +1696,7 @@
     </row>
     <row r="6" s="1" customFormat="1" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>5</v>
@@ -1727,12 +1716,12 @@
         <v>6000</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
@@ -1752,28 +1741,28 @@
         <v>4000</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>60</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C11">
         <f t="shared" ref="C11:C38" si="0">IF(B11&gt;=3500,50,IF(B11&gt;=3000,30,IF(B11&gt;=2500,10,0)))</f>
@@ -1782,7 +1771,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -1791,7 +1780,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -1800,7 +1789,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -1809,7 +1798,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -1818,7 +1807,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -1827,7 +1816,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -1836,7 +1825,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
@@ -1845,7 +1834,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
@@ -1854,7 +1843,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
@@ -1863,7 +1852,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
@@ -1872,7 +1861,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C22">
         <f t="shared" si="0"/>
@@ -1881,7 +1870,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C23">
         <f t="shared" si="0"/>
@@ -1890,7 +1879,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C24">
         <f t="shared" si="0"/>
@@ -1899,7 +1888,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C25">
         <f t="shared" si="0"/>
@@ -1908,7 +1897,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C26">
         <f t="shared" si="0"/>
@@ -1917,7 +1906,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C27">
         <f t="shared" si="0"/>
@@ -1926,7 +1915,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C28">
         <f t="shared" si="0"/>
@@ -1935,7 +1924,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C29">
         <f t="shared" si="0"/>
@@ -1944,7 +1933,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C30">
         <f t="shared" si="0"/>
@@ -1953,7 +1942,7 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C31">
         <f t="shared" si="0"/>
@@ -1962,7 +1951,7 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C32">
         <f t="shared" si="0"/>
@@ -1971,7 +1960,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C33">
         <f t="shared" si="0"/>
@@ -1980,7 +1969,7 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C34">
         <f t="shared" si="0"/>
@@ -1989,7 +1978,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C35">
         <f t="shared" si="0"/>
@@ -1998,7 +1987,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C36">
         <f t="shared" si="0"/>
@@ -2007,7 +1996,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C37">
         <f t="shared" si="0"/>
@@ -2016,7 +2005,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C38">
         <f t="shared" si="0"/>
@@ -2025,7 +2014,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C39" s="3">
         <f>SUM(C11:C38)</f>
@@ -2034,26 +2023,26 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C42" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>62</v>
-      </c>
       <c r="H42" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C43">
         <f t="shared" ref="C43:C70" si="1">IF(B43&gt;=3500,50,IF(B43&gt;=3000,30,IF(B43&gt;=2500,10,0)))</f>
@@ -2062,7 +2051,7 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C44">
         <f t="shared" si="1"/>
@@ -2071,7 +2060,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C45">
         <f t="shared" si="1"/>
@@ -2080,7 +2069,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C46">
         <f t="shared" si="1"/>
@@ -2089,7 +2078,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C47">
         <f t="shared" si="1"/>
@@ -2098,7 +2087,7 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C48">
         <f t="shared" si="1"/>
@@ -2107,7 +2096,7 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C49">
         <f t="shared" si="1"/>
@@ -2116,7 +2105,7 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C50">
         <f t="shared" si="1"/>
@@ -2125,7 +2114,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C51">
         <f t="shared" si="1"/>
@@ -2134,7 +2123,7 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C52">
         <f t="shared" si="1"/>
@@ -2143,7 +2132,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C53">
         <f t="shared" si="1"/>
@@ -2152,7 +2141,7 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C54">
         <f t="shared" si="1"/>
@@ -2161,7 +2150,7 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C55">
         <f t="shared" si="1"/>
@@ -2170,7 +2159,7 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C56">
         <f t="shared" si="1"/>
@@ -2179,7 +2168,7 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C57">
         <f t="shared" si="1"/>
@@ -2188,7 +2177,7 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C58">
         <f t="shared" si="1"/>
@@ -2197,7 +2186,7 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C59">
         <f t="shared" si="1"/>
@@ -2206,7 +2195,7 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C60">
         <f t="shared" si="1"/>
@@ -2215,7 +2204,7 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C61">
         <f t="shared" si="1"/>
@@ -2224,7 +2213,7 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C62">
         <f t="shared" si="1"/>
@@ -2233,7 +2222,7 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C63">
         <f t="shared" si="1"/>
@@ -2242,7 +2231,7 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C64">
         <f t="shared" si="1"/>
@@ -2251,7 +2240,7 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C65">
         <f t="shared" si="1"/>
@@ -2260,7 +2249,7 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C66">
         <f t="shared" si="1"/>
@@ -2269,7 +2258,7 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C67">
         <f t="shared" si="1"/>
@@ -2278,7 +2267,7 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C68">
         <f t="shared" si="1"/>
@@ -2287,7 +2276,7 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C69">
         <f t="shared" si="1"/>
@@ -2296,7 +2285,7 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C70">
         <f t="shared" si="1"/>
@@ -2305,7 +2294,7 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C71" s="3">
         <f>SUM(C43:C70)</f>
@@ -2314,27 +2303,27 @@
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B74" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D74" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="C74" s="8" t="s">
+      <c r="E74" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="D74" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>24</v>
-      </c>
       <c r="H74" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
